--- a/Digital-Business-Toolkit/08-Inventory/Product.xlsx
+++ b/Digital-Business-Toolkit/08-Inventory/Product.xlsx
@@ -7,10 +7,10 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Dashboard" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Main Workspace" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Quick Start" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="User Guide" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="לוח בקרה" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="שולחן עבודה" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="התחלה מהירה" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="מדריך שימוש" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -644,7 +644,7 @@
     <row r="2" ht="46" customHeight="1">
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>Inventory &amp; Materials Manager — Dashboard</t>
+          <t>לוח בקרה — ניהול מלאי וחומרים</t>
         </is>
       </c>
       <c r="C2" s="2" t="n"/>
@@ -655,7 +655,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ContractorOS — Never run out mid-job</t>
+          <t>ContractorOS — לעולם לא תיתקעו בלי חומר באמצע עבודה</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
@@ -692,42 +692,42 @@
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="B6" s="6">
-        <f>SUM('Main Workspace'!H4:H38)</f>
+        <f>SUM('שולחן עבודה'!H4:H38)</f>
         <v/>
       </c>
       <c r="C6" s="6">
-        <f>COUNTA('Main Workspace'!A4:A38)</f>
+        <f>COUNTA('שולחן עבודה'!A4:A38)</f>
         <v/>
       </c>
       <c r="D6" s="6">
-        <f>COUNTIF('Main Workspace'!J4:J38,"מלאי נמוך - להזמין")</f>
+        <f>COUNTIF('שולחן עבודה'!J4:J38,"מלאי נמוך - להזמין")</f>
         <v/>
       </c>
       <c r="E6" s="6">
-        <f>COUNTIF('Main Workspace'!J4:J38,"אזל מהמלאי")</f>
+        <f>COUNTIF('שולחן עבודה'!J4:J38,"אזל מהמלאי")</f>
         <v/>
       </c>
       <c r="F6" s="6">
-        <f>IFERROR(MAX('Main Workspace'!H4:H38),0)</f>
+        <f>IFERROR(MAX('שולחן עבודה'!H4:H38),0)</f>
         <v/>
       </c>
     </row>
     <row r="9" ht="26" customHeight="1">
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>⚠ Business Insights / התראות</t>
+          <t>⚠ תובנות עסקיות והתראות</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1">
       <c r="B10" s="8">
-        <f>IF(COUNTIF('Main Workspace'!J4:J38,"אזל מהמלאי")&gt;0,"יש "&amp;COUNTIF('Main Workspace'!J4:J38,"אזל מהמלאי")&amp;" פריטים שאזלו מהמלאי!","אין פריטים שאזלו מהמלאי.")</f>
+        <f>IF(COUNTIF('שולחן עבודה'!J4:J38,"אזל מהמלאי")&gt;0,"יש "&amp;COUNTIF('שולחן עבודה'!J4:J38,"אזל מהמלאי")&amp;" פריטים שאזלו מהמלאי!","אין פריטים שאזלו מהמלאי.")</f>
         <v/>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1">
       <c r="B11" s="9">
-        <f>IF(COUNTIF('Main Workspace'!J4:J38,"מלאי נמוך - להזמין")&gt;0,"יש "&amp;COUNTIF('Main Workspace'!J4:J38,"מלאי נמוך - להזמין")&amp;" פריטים במלאי נמוך — כדאי להזמין.","כל הפריטים ברמת מלאי תקינה.")</f>
+        <f>IF(COUNTIF('שולחן עבודה'!J4:J38,"מלאי נמוך - להזמין")&gt;0,"יש "&amp;COUNTIF('שולחן עבודה'!J4:J38,"מלאי נמוך - להזמין")&amp;" פריטים במלאי נמוך — כדאי להזמין.","כל הפריטים ברמת מלאי תקינה.")</f>
         <v/>
       </c>
     </row>
@@ -768,7 +768,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>ניהול מלאי וחומרים | Inventory &amp; Materials Manager</t>
+          <t>ניהול מלאי וחומרים</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -800,7 +800,7 @@
     <row r="3" ht="34" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
         <is>
-          <t>SKU</t>
+          <t>מק"ט</t>
         </is>
       </c>
       <c r="B3" s="11" t="inlineStr">
@@ -1654,7 +1654,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>התחלה מהירה | Quick Start</t>
+          <t>התחלה מהירה</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1670,14 +1670,14 @@
     <row r="4" ht="34" customHeight="1">
       <c r="A4" s="21" t="inlineStr">
         <is>
-          <t>1. עברו ללשונית 'Main Workspace'.</t>
+          <t>1. עברו ללשונית 'שולחן עבודה'.</t>
         </is>
       </c>
     </row>
     <row r="6" ht="34" customHeight="1">
       <c r="A6" s="21" t="inlineStr">
         <is>
-          <t>2. הוסיפו שורה לכל פריט מלאי — SKU, שם, קטגוריה, יחידה, כמות, מלאי מינימום, עלות יחידה, ספק.</t>
+          <t>2. הוסיפו שורה לכל פריט מלאי — מק"ט, שם, קטגוריה, יחידה, כמות, מלאי מינימום, עלות יחידה, ספק.</t>
         </is>
       </c>
     </row>
@@ -1698,7 +1698,7 @@
     <row r="12" ht="34" customHeight="1">
       <c r="A12" s="21" t="inlineStr">
         <is>
-          <t>5. עברו ל-Dashboard לראות שווי מלאי כולל ואיזה פריטים דורשים הזמנה.</t>
+          <t>5. עברו ל-לוח הבקרה לראות שווי מלאי כולל ואיזה פריטים דורשים הזמנה.</t>
         </is>
       </c>
     </row>
@@ -1742,7 +1742,7 @@
     <row r="1" ht="44" customHeight="1">
       <c r="A1" s="10" t="inlineStr">
         <is>
-          <t>מדריך שימוש | User Guide</t>
+          <t>מדריך שימוש</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1813,7 +1813,7 @@
       </c>
       <c r="C8" s="24" t="inlineStr">
         <is>
-          <t>SKU, שם פריט, קטגוריה, יחידה, כמות, מלאי מינימום, עלות יחידה, ספק.</t>
+          <t>מק"ט, שם פריט, קטגוריה, יחידה, כמות, מלאי מינימום, עלות יחידה, ספק.</t>
         </is>
       </c>
     </row>
@@ -1832,7 +1832,7 @@
     <row r="10" ht="46" customHeight="1">
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t>מה Dashboard מציג?</t>
+          <t>מה לוח הבקרה מציג?</t>
         </is>
       </c>
       <c r="C10" s="24" t="inlineStr">
@@ -1856,7 +1856,7 @@
     <row r="13">
       <c r="B13" s="25" t="inlineStr">
         <is>
-          <t>שאלות נפוצות (FAQ)</t>
+          <t>שאלות נפוצות</t>
         </is>
       </c>
     </row>

--- a/Digital-Business-Toolkit/08-Inventory/Product.xlsx
+++ b/Digital-Business-Toolkit/08-Inventory/Product.xlsx
@@ -655,7 +655,7 @@
     <row r="3" ht="22" customHeight="1">
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>ContractorOS — לעולם לא תיתקעו בלי חומר באמצע עבודה</t>
+          <t>JobMargin — לעולם לא תיתקעו בלי חומר באמצע עבודה</t>
         </is>
       </c>
       <c r="C3" s="4" t="n"/>
